--- a/data/sankey_simple.xlsx
+++ b/data/sankey_simple.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519CB879-0391-49FF-A8D0-17D106160469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F25957-CBA4-4066-906F-E9B83503C614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8355" yWindow="1440" windowWidth="13020" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2535" yWindow="3615" windowWidth="13020" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -620,7 +620,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="D13" s="1">
         <v>3</v>
@@ -662,7 +662,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="1">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
